--- a/data/SiO2_建模数据.xlsx
+++ b/data/SiO2_建模数据.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD244"/>
+  <dimension ref="A1:AD262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20757,37 +20757,37 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MDL-0009~C</t>
+          <t>MDL-0419</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ1-050924</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -20797,71 +20797,61 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K204" t="n">
-        <v>26.34999999999999</v>
+        <v>30.6</v>
       </c>
       <c r="L204" t="n">
-        <v>0.27987</v>
+        <v>0.67</v>
       </c>
       <c r="M204" t="n">
-        <v>0.478725</v>
+        <v>2.82</v>
       </c>
       <c r="N204" t="n">
-        <v>0.066285</v>
+        <v>0.31</v>
       </c>
       <c r="O204" t="n">
-        <v>1.892805</v>
-      </c>
-      <c r="P204" t="n">
-        <v>4.087575</v>
-      </c>
+        <v>1.092</v>
+      </c>
+      <c r="P204" t="inlineStr"/>
       <c r="Q204" t="n">
-        <v>33.15526</v>
+        <v>35.492</v>
       </c>
       <c r="R204" t="n">
-        <v>73.65000000000001</v>
-      </c>
-      <c r="S204" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="T204" t="n">
-        <v>4.54</v>
-      </c>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
-      <c r="V204" t="n">
-        <v>2</v>
-      </c>
-      <c r="W204" t="n">
-        <v>26</v>
-      </c>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="inlineStr"/>
       <c r="X204" t="n">
-        <v>27.55983</v>
+        <v>41.55</v>
       </c>
       <c r="Y204" t="n">
-        <v>17.712825</v>
+        <v>17.98</v>
       </c>
       <c r="Z204" t="n">
-        <v>17.29302</v>
+        <v>2.93</v>
       </c>
       <c r="AA204" t="n">
-        <v>5.140770000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>converted</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>山西吕梁柳林贾家垣煤矸石</t>
+          <t>美国宾州无烟煤矸石 PA-NCAQ1-050924 RAW</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>补录矿名/产地 | 柳林煤矸石制备生态土/白度研究组（洁净煤技术 2025,31(S1)）</t>
+          <t>第31批(USGS宾州) | PA-NCAQ1-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和98.10</t>
         </is>
       </c>
     </row>
@@ -20871,37 +20861,37 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MDL-0010~C</t>
+          <t>MDL-0420</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ1-050924</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -20911,67 +20901,63 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K205" t="n">
-        <v>13.09999999999999</v>
+        <v>24.68</v>
       </c>
       <c r="L205" t="n">
-        <v>0.59961</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M205" t="n">
-        <v>3.11102</v>
+        <v>2.5</v>
       </c>
       <c r="N205" t="n">
-        <v>0.2954600000000001</v>
+        <v>0.26</v>
       </c>
       <c r="O205" t="n">
-        <v>0.86031</v>
-      </c>
-      <c r="P205" t="n">
-        <v>0.6083</v>
-      </c>
+        <v>0.998</v>
+      </c>
+      <c r="P205" t="inlineStr"/>
       <c r="Q205" t="n">
-        <v>18.57469999999999</v>
+        <v>28.998</v>
       </c>
       <c r="R205" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="S205" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T205" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U205" t="n">
-        <v>51</v>
-      </c>
-      <c r="V205" t="n">
-        <v>1</v>
-      </c>
-      <c r="W205" t="n">
-        <v>11</v>
-      </c>
+        <v>75.31999999999999</v>
+      </c>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
       <c r="X205" t="n">
-        <v>52.10524</v>
+        <v>45.63</v>
       </c>
       <c r="Y205" t="n">
-        <v>20.17818</v>
+        <v>16.87</v>
       </c>
       <c r="Z205" t="n">
-        <v>4.99675</v>
+        <v>7.79</v>
       </c>
       <c r="AA205" t="n">
-        <v>3.84098</v>
+        <v>0.2</v>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr"/>
-      <c r="AD205" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ1-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ1-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.64</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20979,37 +20965,37 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MDL-0011~C</t>
+          <t>MDL-0421</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ2-050924</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -21019,67 +21005,63 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K206" t="n">
-        <v>30.75</v>
+        <v>36.39</v>
       </c>
       <c r="L206" t="n">
-        <v>0.117725</v>
+        <v>0.55</v>
       </c>
       <c r="M206" t="n">
-        <v>0.48475</v>
+        <v>2.11</v>
       </c>
       <c r="N206" t="n">
-        <v>0.07617499999999999</v>
+        <v>0.24</v>
       </c>
       <c r="O206" t="n">
-        <v>1.225725</v>
-      </c>
-      <c r="P206" t="n">
-        <v>0.034625</v>
-      </c>
+        <v>1.231</v>
+      </c>
+      <c r="P206" t="inlineStr"/>
       <c r="Q206" t="n">
-        <v>32.689</v>
+        <v>40.521</v>
       </c>
       <c r="R206" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="S206" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="T206" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="U206" t="n">
-        <v>55</v>
-      </c>
-      <c r="V206" t="n">
-        <v>5</v>
-      </c>
-      <c r="W206" t="n">
-        <v>5</v>
-      </c>
+        <v>63.61</v>
+      </c>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
       <c r="X206" t="n">
-        <v>35.587575</v>
+        <v>33.78</v>
       </c>
       <c r="Y206" t="n">
-        <v>26.5643</v>
+        <v>16.28</v>
       </c>
       <c r="Z206" t="n">
-        <v>4.83365</v>
+        <v>2.15</v>
       </c>
       <c r="AA206" t="n">
-        <v>0.131575</v>
+        <v>6.58</v>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr"/>
-      <c r="AD206" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ2-050924 RAW</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ2-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.40</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21087,37 +21069,37 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MDL-0012~C</t>
+          <t>MDL-0422</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ2-050924</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -21127,67 +21109,63 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K207" t="n">
-        <v>18.20999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="L207" t="n">
-        <v>0.2208330000000001</v>
+        <v>0.864</v>
       </c>
       <c r="M207" t="n">
-        <v>0.458024</v>
+        <v>2.4</v>
       </c>
       <c r="N207" t="n">
-        <v>0.08996900000000001</v>
+        <v>0.36</v>
       </c>
       <c r="O207" t="n">
-        <v>0.8179000000000001</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0.032716</v>
-      </c>
+        <v>1.068</v>
+      </c>
+      <c r="P207" t="inlineStr"/>
       <c r="Q207" t="n">
-        <v>19.82944199999999</v>
+        <v>31.492</v>
       </c>
       <c r="R207" t="n">
-        <v>81.79000000000001</v>
-      </c>
-      <c r="S207" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T207" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U207" t="n">
-        <v>59</v>
-      </c>
-      <c r="V207" t="n">
-        <v>1</v>
-      </c>
-      <c r="W207" t="n">
-        <v>10</v>
-      </c>
+        <v>73.2</v>
+      </c>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
       <c r="X207" t="n">
-        <v>46.37493000000001</v>
+        <v>39.28</v>
       </c>
       <c r="Y207" t="n">
-        <v>32.078038</v>
+        <v>17.39</v>
       </c>
       <c r="Z207" t="n">
-        <v>0.8833320000000002</v>
+        <v>3.39</v>
       </c>
       <c r="AA207" t="n">
-        <v>0.114506</v>
+        <v>7.45</v>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr"/>
-      <c r="AD207" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ2-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ2-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.14</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21195,37 +21173,37 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MDL-0013~C</t>
+          <t>MDL-0423</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ3-050924</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -21235,67 +21213,63 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K208" t="n">
-        <v>36.19</v>
+        <v>35.2</v>
       </c>
       <c r="L208" t="n">
-        <v>0.312669</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M208" t="n">
-        <v>0.7912440000000001</v>
+        <v>1.57</v>
       </c>
       <c r="N208" t="n">
-        <v>0.051048</v>
+        <v>0.24</v>
       </c>
       <c r="O208" t="n">
-        <v>0.344574</v>
-      </c>
-      <c r="P208" t="n">
-        <v>1.391058</v>
-      </c>
+        <v>0.987</v>
+      </c>
+      <c r="P208" t="inlineStr"/>
       <c r="Q208" t="n">
-        <v>39.080593</v>
+        <v>38.557</v>
       </c>
       <c r="R208" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T208" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="U208" t="n">
-        <v>17</v>
-      </c>
-      <c r="V208" t="n">
-        <v>7</v>
-      </c>
-      <c r="W208" t="n">
-        <v>8</v>
-      </c>
+        <v>64.8</v>
+      </c>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
       <c r="X208" t="n">
-        <v>23.399127</v>
+        <v>31.67</v>
       </c>
       <c r="Y208" t="n">
-        <v>9.156734999999999</v>
+        <v>14.41</v>
       </c>
       <c r="Z208" t="n">
-        <v>0.306288</v>
+        <v>4.34</v>
       </c>
       <c r="AA208" t="n">
-        <v>27.94878</v>
+        <v>11.3</v>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr"/>
-      <c r="AD208" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ3-050924 RAW</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ3-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和100.39</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21303,37 +21277,37 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MDL-0014~C</t>
+          <t>MDL-0424</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ3-050924</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -21343,67 +21317,63 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K209" t="n">
-        <v>11</v>
+        <v>38.51</v>
       </c>
       <c r="L209" t="n">
-        <v>0.7565</v>
+        <v>0.52</v>
       </c>
       <c r="M209" t="n">
-        <v>2.7857</v>
+        <v>1.43</v>
       </c>
       <c r="N209" t="n">
-        <v>0.3026</v>
+        <v>0.23</v>
       </c>
       <c r="O209" t="n">
-        <v>1.0057</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0.0178</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="P209" t="inlineStr"/>
       <c r="Q209" t="n">
-        <v>15.8683</v>
+        <v>41.57</v>
       </c>
       <c r="R209" t="n">
-        <v>89</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="U209" t="n">
-        <v>40</v>
-      </c>
-      <c r="V209" t="n">
-        <v>2</v>
-      </c>
-      <c r="W209" t="n">
-        <v>18</v>
-      </c>
+        <v>61.49</v>
+      </c>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
       <c r="X209" t="n">
-        <v>53.7916</v>
+        <v>31.11</v>
       </c>
       <c r="Y209" t="n">
-        <v>25.098</v>
+        <v>13.14</v>
       </c>
       <c r="Z209" t="n">
-        <v>4.7081</v>
+        <v>3.78</v>
       </c>
       <c r="AA209" t="n">
-        <v>0.3115</v>
+        <v>9.69</v>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr"/>
-      <c r="AD209" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ3-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ3-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.39</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21411,37 +21381,37 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MDL-0015~C</t>
+          <t>MDL-0425</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>CSRC-0119</t>
+          <t>USGS-PA-PA-NCAQ4-050924</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>洗矸</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>河东</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -21451,67 +21421,63 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K210" t="n">
-        <v>34.73999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="L210" t="n">
-        <v>0.09136400000000001</v>
+        <v>0.27</v>
       </c>
       <c r="M210" t="n">
-        <v>0.319774</v>
+        <v>1.52</v>
       </c>
       <c r="N210" t="n">
-        <v>0.06526000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="O210" t="n">
-        <v>0.8940620000000001</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0.13052</v>
-      </c>
+        <v>0.635</v>
+      </c>
+      <c r="P210" t="inlineStr"/>
       <c r="Q210" t="n">
-        <v>36.24097999999999</v>
+        <v>54.485</v>
       </c>
       <c r="R210" t="n">
-        <v>65.26000000000001</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T210" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="U210" t="n">
-        <v>66</v>
-      </c>
-      <c r="V210" t="n">
-        <v>1</v>
-      </c>
-      <c r="W210" t="n">
-        <v>3</v>
-      </c>
+        <v>48.2</v>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
       <c r="X210" t="n">
-        <v>35.22082200000001</v>
+        <v>26.7</v>
       </c>
       <c r="Y210" t="n">
-        <v>26.88712</v>
+        <v>11.24</v>
       </c>
       <c r="Z210" t="n">
-        <v>1.213836</v>
+        <v>6.59</v>
       </c>
       <c r="AA210" t="n">
-        <v>0.254514</v>
+        <v>0.04</v>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr"/>
-      <c r="AD210" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ4-050924 RAW</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ4-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.18</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21519,27 +21485,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MDL-0019~C</t>
+          <t>MDL-0426</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CSRC-0113</t>
+          <t>USGS-PA-PA-NCAQ4-050924</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>平凉</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -21549,7 +21515,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>华亭煤田</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -21559,51 +21525,63 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K211" t="n">
-        <v>28.65000000000001</v>
+        <v>50</v>
       </c>
       <c r="L211" t="n">
-        <v>0.18551</v>
+        <v>0.29</v>
       </c>
       <c r="M211" t="n">
-        <v>1.305705</v>
+        <v>1.57</v>
       </c>
       <c r="N211" t="n">
-        <v>0.8633349999999999</v>
-      </c>
-      <c r="O211" t="inlineStr"/>
+        <v>0.27</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0.641</v>
+      </c>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="n">
-        <v>31.00455000000001</v>
-      </c>
-      <c r="R211" t="inlineStr"/>
+        <v>52.771</v>
+      </c>
+      <c r="R211" t="n">
+        <v>50</v>
+      </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" t="inlineStr"/>
       <c r="X211" t="n">
-        <v>30.10256499999999</v>
+        <v>27.11</v>
       </c>
       <c r="Y211" t="n">
-        <v>12.236525</v>
+        <v>11.42</v>
       </c>
       <c r="Z211" t="n">
-        <v>2.547195</v>
+        <v>7.09</v>
       </c>
       <c r="AA211" t="n">
-        <v>9.439604999999998</v>
+        <v>0.32</v>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr"/>
-      <c r="AD211" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ4-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ4-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和98.84</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21611,27 +21589,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MDL-0020~C</t>
+          <t>MDL-0427</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CSRC-0162</t>
+          <t>USGS-PA-PA-NCAQ6-050924</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>六盘水</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -21641,7 +21619,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -21651,59 +21629,63 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>华南P2</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K212" t="n">
-        <v>29.78</v>
+        <v>30.59</v>
       </c>
       <c r="L212" t="n">
-        <v>0.07724199999999999</v>
+        <v>0.64</v>
       </c>
       <c r="M212" t="n">
-        <v>0.14044</v>
+        <v>2.01</v>
       </c>
       <c r="N212" t="n">
-        <v>0.021066</v>
+        <v>0.37</v>
       </c>
       <c r="O212" t="n">
-        <v>1.095432</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0.10533</v>
-      </c>
+        <v>1.039</v>
+      </c>
+      <c r="P212" t="inlineStr"/>
       <c r="Q212" t="n">
-        <v>31.21951</v>
+        <v>34.649</v>
       </c>
       <c r="R212" t="n">
-        <v>70.22</v>
-      </c>
-      <c r="S212" t="n">
-        <v>1.36</v>
-      </c>
+        <v>69.41</v>
+      </c>
+      <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" t="inlineStr"/>
       <c r="X212" t="n">
-        <v>35.959662</v>
+        <v>35.3</v>
       </c>
       <c r="Y212" t="n">
-        <v>28.354836</v>
+        <v>15.23</v>
       </c>
       <c r="Z212" t="n">
-        <v>2.296194</v>
+        <v>5.53</v>
       </c>
       <c r="AA212" t="n">
-        <v>0.17555</v>
+        <v>7.72</v>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr"/>
-      <c r="AD212" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ6-050924 RAW</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ6-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和98.57</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21711,27 +21693,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MDL-0032~C</t>
+          <t>MDL-0428</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CSRC-0156</t>
+          <t>USGS-PA-PA-NCAQ6-050924</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -21741,7 +21723,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -21751,47 +21733,63 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K213" t="n">
-        <v>51.99</v>
+        <v>34.61</v>
       </c>
       <c r="L213" t="n">
-        <v>0.14403</v>
-      </c>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0.969</v>
+      </c>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="n">
-        <v>52.13403</v>
-      </c>
-      <c r="R213" t="inlineStr"/>
+        <v>38.439</v>
+      </c>
+      <c r="R213" t="n">
+        <v>65.39</v>
+      </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" t="inlineStr"/>
       <c r="X213" t="n">
-        <v>23.57291</v>
+        <v>33.74</v>
       </c>
       <c r="Y213" t="n">
-        <v>13.668447</v>
+        <v>14.89</v>
       </c>
       <c r="Z213" t="n">
-        <v>0.206443</v>
+        <v>4.23</v>
       </c>
       <c r="AA213" t="n">
-        <v>0.09121899999999999</v>
+        <v>7.66</v>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr"/>
-      <c r="AD213" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ6-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ6-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.08</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21799,27 +21797,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MDL-0073~C</t>
+          <t>MDL-0429</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CSRC-0194</t>
+          <t>USGS-PA-PA-NCAQ7-050924</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>渭南</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -21829,7 +21827,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>渭北石炭二叠纪煤田</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -21839,59 +21837,63 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K214" t="n">
-        <v>17.17</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L214" t="n">
-        <v>0.654357</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M214" t="n">
-        <v>3.586539</v>
+        <v>2.11</v>
       </c>
       <c r="N214" t="n">
-        <v>0.463848</v>
+        <v>0.5</v>
       </c>
       <c r="O214" t="n">
-        <v>1.201035</v>
+        <v>0.722</v>
       </c>
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="n">
-        <v>23.075779</v>
+        <v>12.102</v>
       </c>
       <c r="R214" t="n">
-        <v>82.83</v>
-      </c>
-      <c r="S214" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="T214" t="n">
-        <v>0.783</v>
-      </c>
+        <v>91.79000000000001</v>
+      </c>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" t="inlineStr"/>
       <c r="X214" t="n">
-        <v>54.386178</v>
+        <v>69</v>
       </c>
       <c r="Y214" t="n">
-        <v>20.144256</v>
+        <v>11.82</v>
       </c>
       <c r="Z214" t="n">
-        <v>1.706298</v>
+        <v>4.97</v>
       </c>
       <c r="AA214" t="n">
-        <v>0.190509</v>
+        <v>0.31</v>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr"/>
-      <c r="AD214" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ7-050924 RAW</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ7-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和98.38</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21899,27 +21901,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MDL-0078~C</t>
+          <t>MDL-0430</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CSRC-0115</t>
+          <t>USGS-PA-PA-NCAQ7-050924</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -21929,65 +21931,73 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>5号煤层</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K215" t="n">
-        <v>12.67</v>
+        <v>7.66</v>
       </c>
       <c r="L215" t="n">
-        <v>0.26199</v>
+        <v>0.6</v>
       </c>
       <c r="M215" t="n">
-        <v>1.082892</v>
+        <v>1.98</v>
       </c>
       <c r="N215" t="n">
-        <v>0.069864</v>
-      </c>
-      <c r="O215" t="inlineStr"/>
+        <v>0.39</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.6840000000000001</v>
+      </c>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="n">
-        <v>14.084746</v>
-      </c>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="n">
-        <v>87.62</v>
-      </c>
+        <v>11.314</v>
+      </c>
+      <c r="R215" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
-      <c r="V215" t="n">
-        <v>1</v>
-      </c>
+      <c r="V215" t="inlineStr"/>
       <c r="W215" t="inlineStr"/>
       <c r="X215" t="n">
-        <v>59.611458</v>
+        <v>71.61</v>
       </c>
       <c r="Y215" t="n">
-        <v>23.832357</v>
+        <v>10.96</v>
       </c>
       <c r="Z215" t="n">
-        <v>1.7466</v>
+        <v>4.59</v>
       </c>
       <c r="AA215" t="n">
-        <v>0.043665</v>
+        <v>0.29</v>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr"/>
-      <c r="AD215" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ7-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ7-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和98.95</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21995,27 +22005,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MDL-0079~C</t>
+          <t>MDL-0431</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CSRC-0115</t>
+          <t>USGS-PA-PA-NCAQ8-050924</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -22025,73 +22035,71 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2号煤层</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K216" t="n">
-        <v>11.19</v>
+        <v>9.19</v>
       </c>
       <c r="L216" t="n">
-        <v>0.9058620000000001</v>
+        <v>1.06</v>
       </c>
       <c r="M216" t="n">
-        <v>1.785081</v>
+        <v>2.9</v>
       </c>
       <c r="N216" t="n">
-        <v>0.222025</v>
+        <v>0.48</v>
       </c>
       <c r="O216" t="n">
-        <v>0.666075</v>
+        <v>0.979</v>
       </c>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="n">
-        <v>14.769043</v>
-      </c>
-      <c r="R216" t="inlineStr"/>
-      <c r="S216" t="n">
-        <v>89.33</v>
-      </c>
+        <v>14.609</v>
+      </c>
+      <c r="R216" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
-      <c r="V216" t="n">
-        <v>1</v>
-      </c>
+      <c r="V216" t="inlineStr"/>
       <c r="W216" t="inlineStr"/>
       <c r="X216" t="n">
-        <v>59.333961</v>
+        <v>58.18</v>
       </c>
       <c r="Y216" t="n">
-        <v>21.465377</v>
+        <v>16.7</v>
       </c>
       <c r="Z216" t="n">
-        <v>3.676734</v>
+        <v>6.92</v>
       </c>
       <c r="AA216" t="n">
-        <v>0.7992900000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>converted</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>小回沟煤矿</t>
+          <t>美国宾州无烟煤矸石 PA-NCAQ8-050924 RAW</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>第十批A回填 | 中煤小回沟煤矿 | 煤炭科学技术 2025,53(6):104-124 表1+表2 | 与在库四元组+LOI完全一致，判为同一数据源；回填矿名/产地/氧化物</t>
+          <t>第31批(USGS宾州) | PA-NCAQ8-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和97.24</t>
         </is>
       </c>
     </row>
@@ -22101,27 +22109,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MDL-0080~C</t>
+          <t>MDL-0432</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CSRC-0115</t>
+          <t>USGS-PA-PA-NCAQ8-050924</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -22131,73 +22139,71 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2号煤层</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K217" t="n">
-        <v>18.92</v>
+        <v>8.82</v>
       </c>
       <c r="L217" t="n">
-        <v>1.021608</v>
+        <v>0.89</v>
       </c>
       <c r="M217" t="n">
-        <v>1.799976</v>
+        <v>2.7</v>
       </c>
       <c r="N217" t="n">
-        <v>0.267564</v>
+        <v>0.47</v>
       </c>
       <c r="O217" t="n">
-        <v>0.5351279999999999</v>
+        <v>0.896</v>
       </c>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="n">
-        <v>22.544276</v>
-      </c>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="n">
-        <v>82.26000000000001</v>
-      </c>
+        <v>13.776</v>
+      </c>
+      <c r="R217" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
-      <c r="V217" t="n">
-        <v>1</v>
-      </c>
+      <c r="V217" t="inlineStr"/>
       <c r="W217" t="inlineStr"/>
       <c r="X217" t="n">
-        <v>48.469624</v>
+        <v>61.08</v>
       </c>
       <c r="Y217" t="n">
-        <v>24.940208</v>
+        <v>16.31</v>
       </c>
       <c r="Z217" t="n">
-        <v>2.813476</v>
+        <v>5.77</v>
       </c>
       <c r="AA217" t="n">
-        <v>0.48648</v>
+        <v>0.38</v>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>converted</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>禾草沟煤矿</t>
+          <t>美国宾州无烟煤矸石 PA-NCAQ8-050924 SINK</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>第十批A回填 | 中煤禾草沟煤矿 | 煤炭科学技术 2025,53(6):104-124 表1+表2 | 与在库四元组+LOI完全一致，判为同一数据源；回填矿名/产地/氧化物</t>
+          <t>第31批(USGS宾州) | PA-NCAQ8-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和97.55</t>
         </is>
       </c>
     </row>
@@ -22207,27 +22213,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MDL-0081~C</t>
+          <t>MDL-0433</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CSRC-0115</t>
+          <t>USGS-PA-PA-NCAQ9-050924</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -22237,73 +22243,71 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>3号煤层</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K218" t="n">
-        <v>10.06</v>
+        <v>35.89</v>
       </c>
       <c r="L218" t="n">
-        <v>1.106262</v>
+        <v>0.49</v>
       </c>
       <c r="M218" t="n">
-        <v>2.392404</v>
+        <v>2.68</v>
       </c>
       <c r="N218" t="n">
-        <v>0.863424</v>
+        <v>0.3</v>
       </c>
       <c r="O218" t="n">
-        <v>0.818454</v>
+        <v>0.926</v>
       </c>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="n">
-        <v>15.240544</v>
-      </c>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="n">
-        <v>90.15000000000001</v>
-      </c>
+        <v>40.286</v>
+      </c>
+      <c r="R218" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
-      <c r="V218" t="n">
-        <v>1</v>
-      </c>
+      <c r="V218" t="inlineStr"/>
       <c r="W218" t="inlineStr"/>
       <c r="X218" t="n">
-        <v>55.92469199999999</v>
+        <v>39.34</v>
       </c>
       <c r="Y218" t="n">
-        <v>27.962346</v>
+        <v>16.88</v>
       </c>
       <c r="Z218" t="n">
-        <v>4.398065999999999</v>
+        <v>2.74</v>
       </c>
       <c r="AA218" t="n">
-        <v>0.305796</v>
+        <v>0.09</v>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>converted</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>白羊岭煤矿</t>
+          <t>美国宾州无烟煤矸石 PA-NCAQ9-050924 RAW</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>第十批A回填 | 中煤白羊岭煤矿 | 煤炭科学技术 2025,53(6):104-124 表1+表2 | 与在库四元组+LOI完全一致，判为同一数据源；回填矿名/产地/氧化物</t>
+          <t>第31批(USGS宾州) | PA-NCAQ9-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.42</t>
         </is>
       </c>
     </row>
@@ -22313,37 +22317,37 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MDL-0090~C</t>
+          <t>MDL-0434</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0001</t>
+          <t>USGS-PA-PA-NCAQ9-050924</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>淮南</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -22353,53 +22357,63 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K219" t="n">
-        <v>12.431</v>
+        <v>27.51</v>
       </c>
       <c r="L219" t="n">
-        <v>0.9632590000000001</v>
+        <v>0.4</v>
       </c>
       <c r="M219" t="n">
-        <v>1.225966</v>
-      </c>
-      <c r="N219" t="inlineStr"/>
+        <v>2.33</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.3</v>
+      </c>
       <c r="O219" t="n">
-        <v>0.788121</v>
+        <v>1.193</v>
       </c>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="n">
-        <v>15.408346</v>
-      </c>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="n">
-        <v>2.98</v>
-      </c>
+        <v>31.733</v>
+      </c>
+      <c r="R219" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" t="inlineStr"/>
       <c r="X219" t="n">
-        <v>52.26117919999999</v>
+        <v>48.17</v>
       </c>
       <c r="Y219" t="n">
-        <v>23.468492</v>
+        <v>17.02</v>
       </c>
       <c r="Z219" t="n">
-        <v>3.677898</v>
+        <v>2.26</v>
       </c>
       <c r="AA219" t="n">
-        <v>2.539501</v>
+        <v>0.08</v>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr"/>
-      <c r="AD219" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ9-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ9-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.33</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22407,37 +22421,37 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MDL-0091~C</t>
+          <t>MDL-0435</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0002</t>
+          <t>USGS-PA-PA-NCAQ10-050924</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>邯郸</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -22447,55 +22461,63 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K220" t="n">
-        <v>10</v>
+        <v>46.11</v>
       </c>
       <c r="L220" t="n">
-        <v>1.017</v>
+        <v>0.46</v>
       </c>
       <c r="M220" t="n">
-        <v>2.331</v>
-      </c>
-      <c r="N220" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0.25</v>
+      </c>
       <c r="O220" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0.3779999999999999</v>
-      </c>
+        <v>0.755</v>
+      </c>
+      <c r="P220" t="inlineStr"/>
       <c r="Q220" t="n">
-        <v>14.698</v>
-      </c>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="n">
-        <v>1.28</v>
-      </c>
+        <v>48.855</v>
+      </c>
+      <c r="R220" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" t="inlineStr"/>
       <c r="X220" t="n">
-        <v>52.731</v>
+        <v>27.11</v>
       </c>
       <c r="Y220" t="n">
-        <v>27.351</v>
+        <v>12.77</v>
       </c>
       <c r="Z220" t="n">
-        <v>3.042</v>
+        <v>2.87</v>
       </c>
       <c r="AA220" t="n">
-        <v>1.233</v>
+        <v>6.96</v>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr"/>
-      <c r="AD220" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ10-050924 RAW</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ10-050924 RAW | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和98.65</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22503,27 +22525,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MDL-0092~C</t>
+          <t>MDL-0436</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0003</t>
+          <t>USGS-PA-PA-NCAQ10-050924</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>乌海</t>
+          <t>宾夕法尼亚</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>矿井煤矸石</t>
+          <t>煤矸石</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -22533,7 +22555,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>Pennsylvania Anthracite</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -22543,51 +22565,63 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K221" t="n">
-        <v>33.47999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="L221" t="n">
-        <v>0.3844856</v>
+        <v>0.48</v>
       </c>
       <c r="M221" t="n">
-        <v>1.051016</v>
-      </c>
-      <c r="N221" t="inlineStr"/>
+        <v>1.41</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0.19</v>
+      </c>
       <c r="O221" t="n">
-        <v>0.8913680000000003</v>
+        <v>0.76</v>
       </c>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="n">
-        <v>35.80686959999999</v>
-      </c>
-      <c r="R221" t="inlineStr"/>
+        <v>40.65000000000001</v>
+      </c>
+      <c r="R221" t="n">
+        <v>62.19</v>
+      </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" t="inlineStr"/>
       <c r="X221" t="n">
-        <v>39.63261600000001</v>
+        <v>35.77</v>
       </c>
       <c r="Y221" t="n">
-        <v>22.77644800000001</v>
+        <v>12.22</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.243924</v>
+        <v>2.38</v>
       </c>
       <c r="AA221" t="n">
-        <v>0.1503352</v>
+        <v>8.09</v>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr"/>
-      <c r="AD221" t="inlineStr"/>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>美国宾州无烟煤矸石 PA-NCAQ10-050924 SINK</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>第31批(USGS宾州) | PA-NCAQ10-050924 SINK | USGS ScienceBase 2024 Table2+Table3(ws基准) | 全项和99.19</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22595,37 +22629,37 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MDL-0098~C</t>
+          <t>MDL-0009~C</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0009</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>原始煤矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -22635,49 +22669,73 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K222" t="n">
-        <v>13.8</v>
+        <v>26.34999999999999</v>
       </c>
       <c r="L222" t="n">
-        <v>0.98268</v>
-      </c>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
+        <v>0.27987</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0.478725</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0.066285</v>
+      </c>
+      <c r="O222" t="n">
+        <v>1.892805</v>
+      </c>
       <c r="P222" t="n">
-        <v>0.37066</v>
+        <v>4.087575</v>
       </c>
       <c r="Q222" t="n">
-        <v>15.15334</v>
-      </c>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr"/>
+        <v>33.15526</v>
+      </c>
+      <c r="R222" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="T222" t="n">
+        <v>4.54</v>
+      </c>
       <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
-      <c r="W222" t="inlineStr"/>
+      <c r="V222" t="n">
+        <v>2</v>
+      </c>
+      <c r="W222" t="n">
+        <v>26</v>
+      </c>
       <c r="X222" t="n">
-        <v>48.47026</v>
+        <v>27.55983</v>
       </c>
       <c r="Y222" t="n">
-        <v>23.85154</v>
+        <v>17.712825</v>
       </c>
       <c r="Z222" t="n">
-        <v>5.61162</v>
+        <v>17.29302</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.72392</v>
+        <v>5.140770000000001</v>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC222" t="inlineStr"/>
-      <c r="AD222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>山西吕梁柳林贾家垣煤矸石</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>补录矿名/产地 | 柳林煤矸石制备生态土/白度研究组（洁净煤技术 2025,31(S1)）</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22685,37 +22743,37 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MDL-0104~C</t>
+          <t>MDL-0010~C</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0015</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -22725,45 +22783,59 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K223" t="n">
-        <v>28.2</v>
+        <v>13.09999999999999</v>
       </c>
       <c r="L223" t="n">
-        <v>0.25848</v>
-      </c>
-      <c r="M223" t="inlineStr"/>
+        <v>0.59961</v>
+      </c>
+      <c r="M223" t="n">
+        <v>3.11102</v>
+      </c>
       <c r="N223" t="n">
-        <v>0.01436</v>
+        <v>0.2954600000000001</v>
       </c>
       <c r="O223" t="n">
-        <v>0.8615999999999999</v>
+        <v>0.86031</v>
       </c>
       <c r="P223" t="n">
-        <v>1.19906</v>
+        <v>0.6083</v>
       </c>
       <c r="Q223" t="n">
-        <v>30.5335</v>
-      </c>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
-      <c r="T223" t="inlineStr"/>
-      <c r="U223" t="inlineStr"/>
-      <c r="V223" t="inlineStr"/>
-      <c r="W223" t="inlineStr"/>
+        <v>18.57469999999999</v>
+      </c>
+      <c r="R223" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="S223" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U223" t="n">
+        <v>51</v>
+      </c>
+      <c r="V223" t="n">
+        <v>1</v>
+      </c>
+      <c r="W223" t="n">
+        <v>11</v>
+      </c>
       <c r="X223" t="n">
-        <v>33.25776</v>
+        <v>52.10524</v>
       </c>
       <c r="Y223" t="n">
-        <v>32.55412</v>
+        <v>20.17818</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.62466</v>
+        <v>4.99675</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.60114</v>
+        <v>3.84098</v>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
@@ -22779,27 +22851,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MDL-0107~C</t>
+          <t>MDL-0011~C</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0018</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -22809,7 +22881,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -22819,41 +22891,59 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K224" t="n">
-        <v>15.40000000000001</v>
+        <v>30.75</v>
       </c>
       <c r="L224" t="n">
-        <v>0.7529399999999999</v>
-      </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
+        <v>0.117725</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0.07617499999999999</v>
+      </c>
       <c r="O224" t="n">
-        <v>0.40608</v>
-      </c>
-      <c r="P224" t="inlineStr"/>
+        <v>1.225725</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0.034625</v>
+      </c>
       <c r="Q224" t="n">
-        <v>16.55902</v>
-      </c>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
-      <c r="T224" t="inlineStr"/>
-      <c r="U224" t="inlineStr"/>
-      <c r="V224" t="inlineStr"/>
-      <c r="W224" t="inlineStr"/>
+        <v>32.689</v>
+      </c>
+      <c r="R224" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T224" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="U224" t="n">
+        <v>55</v>
+      </c>
+      <c r="V224" t="n">
+        <v>5</v>
+      </c>
+      <c r="W224" t="n">
+        <v>5</v>
+      </c>
       <c r="X224" t="n">
-        <v>51.85134</v>
+        <v>35.587575</v>
       </c>
       <c r="Y224" t="n">
-        <v>9.796679999999999</v>
+        <v>26.5643</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.99656</v>
+        <v>4.83365</v>
       </c>
       <c r="AA224" t="n">
-        <v>8.045459999999999</v>
+        <v>0.131575</v>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
@@ -22869,37 +22959,37 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MDL-0109~C</t>
+          <t>MDL-0012~C</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0019</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>淮南</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -22913,43 +23003,55 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>13.64</v>
+        <v>18.20999999999999</v>
       </c>
       <c r="L225" t="n">
-        <v>3.963924</v>
+        <v>0.2208330000000001</v>
       </c>
       <c r="M225" t="n">
-        <v>1.2859004</v>
+        <v>0.458024</v>
       </c>
       <c r="N225" t="n">
-        <v>0.4214367999999999</v>
-      </c>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
+        <v>0.08996900000000001</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0.8179000000000001</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.032716</v>
+      </c>
       <c r="Q225" t="n">
-        <v>19.3112612</v>
+        <v>19.82944199999999</v>
       </c>
       <c r="R225" t="n">
-        <v>86.36</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="S225" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T225" t="inlineStr"/>
-      <c r="U225" t="inlineStr"/>
-      <c r="V225" t="inlineStr"/>
-      <c r="W225" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="T225" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U225" t="n">
+        <v>59</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1</v>
+      </c>
+      <c r="W225" t="n">
+        <v>10</v>
+      </c>
       <c r="X225" t="n">
-        <v>51.4083808</v>
+        <v>46.37493000000001</v>
       </c>
       <c r="Y225" t="n">
-        <v>19.7781672</v>
+        <v>32.078038</v>
       </c>
       <c r="Z225" t="n">
-        <v>7.555636400000001</v>
+        <v>0.8833320000000002</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.4111224</v>
+        <v>0.114506</v>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
@@ -22965,37 +23067,37 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MDL-0112~C</t>
+          <t>MDL-0013~C</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0019</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -23005,39 +23107,59 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K226" t="n">
-        <v>26.98999999999999</v>
-      </c>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
+        <v>36.19</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.312669</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0.7912440000000001</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0.051048</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0.344574</v>
+      </c>
+      <c r="P226" t="n">
+        <v>1.391058</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>39.080593</v>
+      </c>
       <c r="R226" t="n">
-        <v>73.01000000000001</v>
+        <v>63.81</v>
       </c>
       <c r="S226" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T226" t="inlineStr"/>
-      <c r="U226" t="inlineStr"/>
-      <c r="V226" t="inlineStr"/>
-      <c r="W226" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="T226" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="U226" t="n">
+        <v>17</v>
+      </c>
+      <c r="V226" t="n">
+        <v>7</v>
+      </c>
+      <c r="W226" t="n">
+        <v>8</v>
+      </c>
       <c r="X226" t="n">
-        <v>39.5531675</v>
+        <v>23.399127</v>
       </c>
       <c r="Y226" t="n">
-        <v>13.8872321</v>
+        <v>9.156734999999999</v>
       </c>
       <c r="Z226" t="n">
-        <v>2.5487791</v>
+        <v>0.306288</v>
       </c>
       <c r="AA226" t="n">
-        <v>1.0082681</v>
+        <v>27.94878</v>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
@@ -23053,12 +23175,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>MDL-0113~C</t>
+          <t>MDL-0014~C</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0019</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -23068,22 +23190,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -23097,35 +23219,55 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>42.72</v>
-      </c>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="M227" t="n">
+        <v>2.7857</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="O227" t="n">
+        <v>1.0057</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>15.8683</v>
+      </c>
       <c r="R227" t="n">
-        <v>57.28</v>
+        <v>89</v>
       </c>
       <c r="S227" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T227" t="inlineStr"/>
-      <c r="U227" t="inlineStr"/>
-      <c r="V227" t="inlineStr"/>
-      <c r="W227" t="inlineStr"/>
+        <v>0.65</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="U227" t="n">
+        <v>40</v>
+      </c>
+      <c r="V227" t="n">
+        <v>2</v>
+      </c>
+      <c r="W227" t="n">
+        <v>18</v>
+      </c>
       <c r="X227" t="n">
-        <v>27.921136</v>
+        <v>53.7916</v>
       </c>
       <c r="Y227" t="n">
-        <v>15.4106112</v>
+        <v>25.098</v>
       </c>
       <c r="Z227" t="n">
-        <v>1.4829792</v>
+        <v>4.7081</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.9703231999999999</v>
+        <v>0.3115</v>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
@@ -23141,12 +23283,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MDL-0114~C</t>
+          <t>MDL-0015~C</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0019</t>
+          <t>CSRC-0119</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -23156,22 +23298,22 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>吕梁</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>洗矸</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>河东</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -23185,35 +23327,55 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
+        <v>34.73999999999999</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.09136400000000001</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0.319774</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0.06526000000000001</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0.8940620000000001</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0.13052</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>36.24097999999999</v>
+      </c>
       <c r="R228" t="n">
-        <v>80.2</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="S228" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr"/>
-      <c r="V228" t="inlineStr"/>
-      <c r="W228" t="inlineStr"/>
+        <v>0.55</v>
+      </c>
+      <c r="T228" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="U228" t="n">
+        <v>66</v>
+      </c>
+      <c r="V228" t="n">
+        <v>1</v>
+      </c>
+      <c r="W228" t="n">
+        <v>3</v>
+      </c>
       <c r="X228" t="n">
-        <v>41.577284</v>
+        <v>35.22082200000001</v>
       </c>
       <c r="Y228" t="n">
-        <v>17.683298</v>
+        <v>26.88712</v>
       </c>
       <c r="Z228" t="n">
-        <v>5.857808</v>
+        <v>1.213836</v>
       </c>
       <c r="AA228" t="n">
-        <v>1.55187</v>
+        <v>0.254514</v>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
@@ -23229,27 +23391,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MDL-0117~C</t>
+          <t>MDL-0019~C</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CSRC-EXP-0021</t>
+          <t>CSRC-0113</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>鄂尔多斯</t>
+          <t>平凉</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -23259,7 +23421,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>华亭煤田</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -23273,23 +23435,21 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>25.69</v>
+        <v>28.65000000000001</v>
       </c>
       <c r="L229" t="n">
-        <v>0.364119</v>
+        <v>0.18551</v>
       </c>
       <c r="M229" t="n">
-        <v>0.423567</v>
-      </c>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="n">
-        <v>0.9140130000000001</v>
-      </c>
-      <c r="P229" t="n">
-        <v>0.8991509999999999</v>
-      </c>
+        <v>1.305705</v>
+      </c>
+      <c r="N229" t="n">
+        <v>0.8633349999999999</v>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
       <c r="Q229" t="n">
-        <v>28.29085</v>
+        <v>31.00455000000001</v>
       </c>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
@@ -23298,16 +23458,16 @@
       <c r="V229" t="inlineStr"/>
       <c r="W229" t="inlineStr"/>
       <c r="X229" t="n">
-        <v>32.458608</v>
+        <v>30.10256499999999</v>
       </c>
       <c r="Y229" t="n">
-        <v>36.679416</v>
+        <v>12.236525</v>
       </c>
       <c r="Z229" t="n">
-        <v>0.490446</v>
+        <v>2.547195</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.092357</v>
+        <v>9.439604999999998</v>
       </c>
       <c r="AB229" t="inlineStr">
         <is>
@@ -23323,32 +23483,32 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MDL-0132~C</t>
+          <t>MDL-0020~C</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CSRC-0120</t>
+          <t>CSRC-0162</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>朔州</t>
+          <t>六盘水</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -23363,49 +23523,51 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>华南P2</t>
         </is>
       </c>
       <c r="K230" t="n">
-        <v>32.3</v>
+        <v>29.78</v>
       </c>
       <c r="L230" t="n">
-        <v>0.3385</v>
+        <v>0.07724199999999999</v>
       </c>
       <c r="M230" t="n">
-        <v>0.2031</v>
-      </c>
-      <c r="N230" t="inlineStr"/>
+        <v>0.14044</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0.021066</v>
+      </c>
       <c r="O230" t="n">
-        <v>0.6093000000000001</v>
-      </c>
-      <c r="P230" t="inlineStr"/>
+        <v>1.095432</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.10533</v>
+      </c>
       <c r="Q230" t="n">
-        <v>33.4509</v>
+        <v>31.21951</v>
       </c>
       <c r="R230" t="n">
-        <v>67.7</v>
+        <v>70.22</v>
       </c>
       <c r="S230" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T230" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>1.36</v>
+      </c>
+      <c r="T230" t="inlineStr"/>
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" t="inlineStr"/>
       <c r="X230" t="n">
-        <v>40.5523</v>
+        <v>35.959662</v>
       </c>
       <c r="Y230" t="n">
-        <v>21.4609</v>
+        <v>28.354836</v>
       </c>
       <c r="Z230" t="n">
-        <v>1.6925</v>
+        <v>2.296194</v>
       </c>
       <c r="AA230" t="n">
-        <v>2.0987</v>
+        <v>0.17555</v>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
@@ -23421,12 +23583,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MDL-0133~C</t>
+          <t>MDL-0032~C</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CSRC-0120</t>
+          <t>CSRC-0156</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -23436,17 +23598,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>忻州</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -23465,45 +23627,35 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>28.2</v>
+        <v>51.99</v>
       </c>
       <c r="L231" t="n">
-        <v>0.2154</v>
-      </c>
-      <c r="M231" t="n">
-        <v>1.436</v>
-      </c>
+        <v>0.14403</v>
+      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
-      <c r="O231" t="n">
-        <v>0.5744</v>
-      </c>
+      <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
       <c r="Q231" t="n">
-        <v>30.4258</v>
-      </c>
-      <c r="R231" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="S231" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T231" t="n">
-        <v>6.7</v>
-      </c>
+        <v>52.13403</v>
+      </c>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" t="inlineStr"/>
       <c r="X231" t="n">
-        <v>41.1414</v>
+        <v>23.57291</v>
       </c>
       <c r="Y231" t="n">
-        <v>16.2986</v>
+        <v>13.668447</v>
       </c>
       <c r="Z231" t="n">
-        <v>3.1592</v>
+        <v>0.206443</v>
       </c>
       <c r="AA231" t="n">
-        <v>6.6774</v>
+        <v>0.09121899999999999</v>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
@@ -23519,37 +23671,37 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MDL-0134~C</t>
+          <t>MDL-0073~C</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CSRC-0120</t>
+          <t>CSRC-0194</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>吕梁</t>
+          <t>渭南</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>渭北石炭二叠纪煤田</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -23559,51 +23711,51 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>西北J</t>
         </is>
       </c>
       <c r="K232" t="n">
-        <v>31</v>
+        <v>17.17</v>
       </c>
       <c r="L232" t="n">
-        <v>0.345</v>
+        <v>0.654357</v>
       </c>
       <c r="M232" t="n">
-        <v>0.897</v>
+        <v>3.586539</v>
       </c>
       <c r="N232" t="n">
-        <v>0.138</v>
+        <v>0.463848</v>
       </c>
       <c r="O232" t="n">
-        <v>1.104</v>
+        <v>1.201035</v>
       </c>
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="n">
-        <v>33.484</v>
+        <v>23.075779</v>
       </c>
       <c r="R232" t="n">
-        <v>69</v>
+        <v>82.83</v>
       </c>
       <c r="S232" t="n">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="T232" t="n">
-        <v>7.7</v>
+        <v>0.783</v>
       </c>
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" t="inlineStr"/>
       <c r="X232" t="n">
-        <v>39.054</v>
+        <v>54.386178</v>
       </c>
       <c r="Y232" t="n">
-        <v>24.771</v>
+        <v>20.144256</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.725</v>
+        <v>1.706298</v>
       </c>
       <c r="AA232" t="n">
-        <v>0.138</v>
+        <v>0.190509</v>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
@@ -23619,32 +23771,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MDL-0135~C</t>
+          <t>MDL-0078~C</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CSRC-0120</t>
+          <t>CSRC-0115</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>晋中</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -23654,54 +23806,52 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>5号煤层</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>西北J</t>
         </is>
       </c>
       <c r="K233" t="n">
-        <v>26.90000000000001</v>
+        <v>12.67</v>
       </c>
       <c r="L233" t="n">
-        <v>0.3655</v>
+        <v>0.26199</v>
       </c>
       <c r="M233" t="n">
-        <v>0.8771999999999999</v>
-      </c>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="n">
-        <v>0.8771999999999999</v>
-      </c>
+        <v>1.082892</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0.069864</v>
+      </c>
+      <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="n">
-        <v>29.01990000000001</v>
-      </c>
-      <c r="R233" t="n">
-        <v>73.09999999999999</v>
-      </c>
+        <v>14.084746</v>
+      </c>
+      <c r="R233" t="inlineStr"/>
       <c r="S233" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T233" t="n">
-        <v>6.6</v>
-      </c>
+        <v>87.62</v>
+      </c>
+      <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
-      <c r="V233" t="inlineStr"/>
+      <c r="V233" t="n">
+        <v>1</v>
+      </c>
       <c r="W233" t="inlineStr"/>
       <c r="X233" t="n">
-        <v>46.1992</v>
+        <v>59.611458</v>
       </c>
       <c r="Y233" t="n">
-        <v>17.2516</v>
+        <v>23.832357</v>
       </c>
       <c r="Z233" t="n">
-        <v>4.824599999999999</v>
+        <v>1.7466</v>
       </c>
       <c r="AA233" t="n">
-        <v>1.2427</v>
+        <v>0.043665</v>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
@@ -23717,12 +23867,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MDL-0136~C</t>
+          <t>MDL-0079~C</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CSRC-0120</t>
+          <t>CSRC-0115</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -23732,17 +23882,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>长治</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -23752,7 +23902,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>2号煤层</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -23761,55 +23911,61 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>35.09999999999999</v>
+        <v>11.19</v>
       </c>
       <c r="L234" t="n">
-        <v>1.4278</v>
+        <v>0.9058620000000001</v>
       </c>
       <c r="M234" t="n">
-        <v>1.1682</v>
+        <v>1.785081</v>
       </c>
       <c r="N234" t="n">
-        <v>0.3245</v>
+        <v>0.222025</v>
       </c>
       <c r="O234" t="n">
-        <v>0.7139000000000002</v>
+        <v>0.666075</v>
       </c>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="n">
-        <v>38.73439999999999</v>
-      </c>
-      <c r="R234" t="n">
-        <v>64.90000000000001</v>
-      </c>
+        <v>14.769043</v>
+      </c>
+      <c r="R234" t="inlineStr"/>
       <c r="S234" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T234" t="n">
-        <v>9.5</v>
-      </c>
+        <v>89.33</v>
+      </c>
+      <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr"/>
+      <c r="V234" t="n">
+        <v>1</v>
+      </c>
       <c r="W234" t="inlineStr"/>
       <c r="X234" t="n">
-        <v>35.69500000000001</v>
+        <v>59.333961</v>
       </c>
       <c r="Y234" t="n">
-        <v>18.8859</v>
+        <v>21.465377</v>
       </c>
       <c r="Z234" t="n">
-        <v>1.7523</v>
+        <v>3.676734</v>
       </c>
       <c r="AA234" t="n">
-        <v>3.6993</v>
+        <v>0.7992900000000001</v>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr"/>
-      <c r="AD234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>小回沟煤矿</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>第十批A回填 | 中煤小回沟煤矿 | 煤炭科学技术 2025,53(6):104-124 表1+表2 | 与在库四元组+LOI完全一致，判为同一数据源；回填矿名/产地/氧化物</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23817,32 +23973,32 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MDL-0137~C</t>
+          <t>MDL-0080~C</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CSRC-0120</t>
+          <t>CSRC-0115</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>临汾</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>洗选矸石</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>WASHED_GANGUE</t>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -23852,64 +24008,70 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>2号煤层</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>西北J</t>
         </is>
       </c>
       <c r="K235" t="n">
-        <v>14.09999999999999</v>
+        <v>18.92</v>
       </c>
       <c r="L235" t="n">
-        <v>0.4295</v>
+        <v>1.021608</v>
       </c>
       <c r="M235" t="n">
-        <v>2.0616</v>
+        <v>1.799976</v>
       </c>
       <c r="N235" t="n">
-        <v>0.2577</v>
+        <v>0.267564</v>
       </c>
       <c r="O235" t="n">
-        <v>0.9449000000000001</v>
+        <v>0.5351279999999999</v>
       </c>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="n">
-        <v>17.79369999999999</v>
-      </c>
-      <c r="R235" t="n">
-        <v>85.90000000000001</v>
-      </c>
+        <v>22.544276</v>
+      </c>
+      <c r="R235" t="inlineStr"/>
       <c r="S235" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T235" t="n">
-        <v>1.1</v>
-      </c>
+        <v>82.26000000000001</v>
+      </c>
+      <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr"/>
-      <c r="V235" t="inlineStr"/>
+      <c r="V235" t="n">
+        <v>1</v>
+      </c>
       <c r="W235" t="inlineStr"/>
       <c r="X235" t="n">
-        <v>54.20290000000001</v>
+        <v>48.469624</v>
       </c>
       <c r="Y235" t="n">
-        <v>24.13790000000001</v>
+        <v>24.940208</v>
       </c>
       <c r="Z235" t="n">
-        <v>2.0616</v>
+        <v>2.813476</v>
       </c>
       <c r="AA235" t="n">
-        <v>0.8590000000000001</v>
+        <v>0.48648</v>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr"/>
-      <c r="AD235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>禾草沟煤矿</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>第十批A回填 | 中煤禾草沟煤矿 | 煤炭科学技术 2025,53(6):104-124 表1+表2 | 与在库四元组+LOI完全一致，判为同一数据源；回填矿名/产地/氧化物</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23917,27 +24079,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MDL-0138~C</t>
+          <t>MDL-0081~C</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>CSRC-NEW-LPS-2014</t>
+          <t>CSRC-0115</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>六盘水</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+          <t>混合/未说明</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -23952,70 +24114,70 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>3号煤层</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>华南P2</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K236" t="n">
-        <v>29.87</v>
+        <v>10.06</v>
       </c>
       <c r="L236" t="n">
-        <v>0.673248</v>
+        <v>1.106262</v>
       </c>
       <c r="M236" t="n">
-        <v>0.715326</v>
+        <v>2.392404</v>
       </c>
       <c r="N236" t="n">
-        <v>0.294546</v>
+        <v>0.863424</v>
       </c>
       <c r="O236" t="n">
-        <v>1.802341</v>
+        <v>0.818454</v>
       </c>
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="n">
-        <v>33.35546100000001</v>
-      </c>
-      <c r="R236" t="n">
-        <v>70.13</v>
-      </c>
+        <v>15.240544</v>
+      </c>
+      <c r="R236" t="inlineStr"/>
       <c r="S236" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T236" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U236" t="n">
-        <v>23.34</v>
-      </c>
+        <v>90.15000000000001</v>
+      </c>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
       <c r="V236" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="W236" t="n">
-        <v>50.06</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W236" t="inlineStr"/>
       <c r="X236" t="n">
-        <v>29.672003</v>
+        <v>55.92469199999999</v>
       </c>
       <c r="Y236" t="n">
-        <v>15.190158</v>
+        <v>27.962346</v>
       </c>
       <c r="Z236" t="n">
-        <v>5.477152999999999</v>
+        <v>4.398065999999999</v>
       </c>
       <c r="AA236" t="n">
-        <v>1.598964</v>
+        <v>0.305796</v>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC236" t="inlineStr"/>
-      <c r="AD236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>白羊岭煤矿</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>第十批A回填 | 中煤白羊岭煤矿 | 煤炭科学技术 2025,53(6):104-124 表1+表2 | 与在库四元组+LOI完全一致，判为同一数据源；回填矿名/产地/氧化物</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24023,32 +24185,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MDL-0139~C</t>
+          <t>MDL-0090~C</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CSRC-NEW-LPS-2014</t>
+          <t>CSRC-EXP-0001</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>六盘水</t>
+          <t>淮南</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+          <t>洗选矸石</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -24063,57 +24225,45 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>华南P2</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K237" t="n">
-        <v>32.27</v>
+        <v>12.431</v>
       </c>
       <c r="L237" t="n">
-        <v>1.192048</v>
+        <v>0.9632590000000001</v>
       </c>
       <c r="M237" t="n">
-        <v>0.6434350000000001</v>
-      </c>
-      <c r="N237" t="n">
-        <v>0.8804900000000001</v>
-      </c>
+        <v>1.225966</v>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="O237" t="n">
-        <v>2.329912</v>
+        <v>0.788121</v>
       </c>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="n">
-        <v>37.31588499999999</v>
-      </c>
-      <c r="R237" t="n">
-        <v>67.73</v>
-      </c>
+        <v>15.408346</v>
+      </c>
+      <c r="R237" t="inlineStr"/>
       <c r="S237" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T237" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U237" t="n">
-        <v>8</v>
-      </c>
-      <c r="V237" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W237" t="n">
-        <v>25.63</v>
-      </c>
+        <v>2.98</v>
+      </c>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr"/>
+      <c r="W237" t="inlineStr"/>
       <c r="X237" t="n">
-        <v>28.466919</v>
+        <v>52.26117919999999</v>
       </c>
       <c r="Y237" t="n">
-        <v>11.818885</v>
+        <v>23.468492</v>
       </c>
       <c r="Z237" t="n">
-        <v>7.748311999999999</v>
+        <v>3.677898</v>
       </c>
       <c r="AA237" t="n">
-        <v>3.122353</v>
+        <v>2.539501</v>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
@@ -24129,32 +24279,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MDL-0140~C</t>
+          <t>MDL-0091~C</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CSRC-NEW-LPS-2014</t>
+          <t>CSRC-EXP-0002</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>六盘水</t>
+          <t>邯郸</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+          <t>洗选矸石</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -24169,57 +24319,47 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>华南P2</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K238" t="n">
-        <v>20.70999999999999</v>
+        <v>10</v>
       </c>
       <c r="L238" t="n">
-        <v>0.8484030000000001</v>
+        <v>1.017</v>
       </c>
       <c r="M238" t="n">
-        <v>1.292427</v>
-      </c>
-      <c r="N238" t="n">
-        <v>0.126864</v>
-      </c>
+        <v>2.331</v>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="O238" t="n">
-        <v>0.6184620000000001</v>
-      </c>
-      <c r="P238" t="inlineStr"/>
+        <v>0.972</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0.3779999999999999</v>
+      </c>
       <c r="Q238" t="n">
-        <v>23.59615599999999</v>
-      </c>
-      <c r="R238" t="n">
-        <v>79.29000000000001</v>
-      </c>
+        <v>14.698</v>
+      </c>
+      <c r="R238" t="inlineStr"/>
       <c r="S238" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T238" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U238" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V238" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W238" t="n">
-        <v>92.56999999999999</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr"/>
+      <c r="W238" t="inlineStr"/>
       <c r="X238" t="n">
-        <v>44.695773</v>
+        <v>52.731</v>
       </c>
       <c r="Y238" t="n">
-        <v>16.325811</v>
+        <v>27.351</v>
       </c>
       <c r="Z238" t="n">
-        <v>3.33018</v>
+        <v>3.042</v>
       </c>
       <c r="AA238" t="n">
-        <v>0.261657</v>
+        <v>1.233</v>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
@@ -24235,27 +24375,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MDL-0141~C</t>
+          <t>MDL-0092~C</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CSRC-NEW-LPS-2014</t>
+          <t>CSRC-EXP-0003</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>六盘水</t>
+          <t>乌海</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+          <t>矿井煤矸石</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -24275,55 +24415,43 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>华南P2</t>
+          <t>西北J</t>
         </is>
       </c>
       <c r="K239" t="n">
-        <v>27.73999999999999</v>
+        <v>33.47999999999999</v>
       </c>
       <c r="L239" t="n">
-        <v>0.852668</v>
+        <v>0.3844856</v>
       </c>
       <c r="M239" t="n">
-        <v>1.546364</v>
-      </c>
-      <c r="N239" t="n">
-        <v>0.115616</v>
-      </c>
+        <v>1.051016</v>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="O239" t="n">
-        <v>1.828178</v>
+        <v>0.8913680000000003</v>
       </c>
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="n">
-        <v>32.082826</v>
-      </c>
-      <c r="R239" t="n">
-        <v>72.26000000000001</v>
-      </c>
-      <c r="S239" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T239" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U239" t="n">
-        <v>4.86</v>
-      </c>
+        <v>35.80686959999999</v>
+      </c>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
-      <c r="W239" t="n">
-        <v>24.67</v>
-      </c>
+      <c r="W239" t="inlineStr"/>
       <c r="X239" t="n">
-        <v>27.480478</v>
+        <v>39.63261600000001</v>
       </c>
       <c r="Y239" t="n">
-        <v>11.135266</v>
+        <v>22.77644800000001</v>
       </c>
       <c r="Z239" t="n">
-        <v>14.784396</v>
+        <v>1.243924</v>
       </c>
       <c r="AA239" t="n">
-        <v>1.091126</v>
+        <v>0.1503352</v>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
@@ -24339,27 +24467,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MDL-0176~C</t>
+          <t>MDL-0098~C</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CSRC-REM-0018</t>
+          <t>CSRC-EXP-0009</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>焦作</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>混合/未说明</t>
+          <t>原始煤矸石</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -24379,41 +24507,41 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K240" t="n">
-        <v>86.19</v>
-      </c>
-      <c r="L240" t="inlineStr"/>
+        <v>13.8</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0.98268</v>
+      </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="n">
-        <v>13.81</v>
-      </c>
-      <c r="S240" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T240" t="n">
-        <v>17.48</v>
-      </c>
+      <c r="P240" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>15.15334</v>
+      </c>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" t="inlineStr"/>
       <c r="X240" t="n">
-        <v>6.947811000000001</v>
+        <v>48.47026</v>
       </c>
       <c r="Y240" t="n">
-        <v>5.631718000000001</v>
+        <v>23.85154</v>
       </c>
       <c r="Z240" t="n">
-        <v>0.549638</v>
+        <v>5.61162</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.319011</v>
+        <v>2.72392</v>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
@@ -24429,22 +24557,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MDL-0391~C</t>
+          <t>MDL-0104~C</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CSRC-ASH-002</t>
+          <t>CSRC-EXP-0015</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>晋中</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -24469,63 +24597,53 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>华北C-P</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K241" t="n">
-        <v>27.27</v>
+        <v>28.2</v>
       </c>
       <c r="L241" t="n">
-        <v>0.14546</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0.4654720000000001</v>
-      </c>
+        <v>0.25848</v>
+      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="n">
-        <v>0.029092</v>
+        <v>0.01436</v>
       </c>
       <c r="O241" t="n">
-        <v>0.43638</v>
-      </c>
-      <c r="P241" t="inlineStr"/>
+        <v>0.8615999999999999</v>
+      </c>
+      <c r="P241" t="n">
+        <v>1.19906</v>
+      </c>
       <c r="Q241" t="n">
-        <v>28.346404</v>
-      </c>
-      <c r="R241" t="n">
-        <v>72.73</v>
-      </c>
+        <v>30.5335</v>
+      </c>
+      <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" t="inlineStr"/>
       <c r="X241" t="n">
-        <v>37.67414</v>
+        <v>33.25776</v>
       </c>
       <c r="Y241" t="n">
-        <v>21.542626</v>
+        <v>32.55412</v>
       </c>
       <c r="Z241" t="n">
-        <v>0.458199</v>
+        <v>0.62466</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.09454900000000001</v>
+        <v>1.60114</v>
       </c>
       <c r="AB241" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>灵石县永恒煤化（9#/10#煤洗矸）</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>灰基准回收 | 表3-5工业(Ad72.73)+表3-6化学；四目标和82.18&gt;灰分+2 → 灰基准</t>
-        </is>
-      </c>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24533,32 +24651,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MDL-0392~C</t>
+          <t>MDL-0107~C</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CSRC-ASH-003</t>
+          <t>CSRC-EXP-0018</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>咸阳</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>煤矸石</t>
+          <t>洗选矸石</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+          <t>WASHED_GANGUE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -24573,59 +24691,49 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>西北J</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K242" t="n">
-        <v>37.25</v>
+        <v>15.40000000000001</v>
       </c>
       <c r="L242" t="n">
-        <v>0.69025</v>
+        <v>0.7529399999999999</v>
       </c>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.40608</v>
       </c>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="n">
-        <v>38.81875</v>
-      </c>
-      <c r="R242" t="n">
-        <v>62.75</v>
-      </c>
+        <v>16.55902</v>
+      </c>
+      <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" t="inlineStr"/>
       <c r="X242" t="n">
-        <v>41.72875</v>
+        <v>51.85134</v>
       </c>
       <c r="Y242" t="n">
-        <v>12.9265</v>
+        <v>9.796679999999999</v>
       </c>
       <c r="Z242" t="n">
-        <v>4.83175</v>
+        <v>1.99656</v>
       </c>
       <c r="AA242" t="n">
-        <v>1.69425</v>
+        <v>8.045459999999999</v>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>彬州陈家坪制砂原料矸</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>灰基准回收 | 灰分62.75+烧失量26.5；四目标和97.5&gt;灰分+2 → 灰基准</t>
-        </is>
-      </c>
+      <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24633,22 +24741,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MDL-0393~C</t>
+          <t>MDL-0109~C</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>CSRC-ASH-004</t>
+          <t>CSRC-EXP-0019</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>淮南</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -24673,65 +24781,55 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>华北C-P</t>
         </is>
       </c>
       <c r="K243" t="n">
-        <v>14.75</v>
+        <v>13.64</v>
       </c>
       <c r="L243" t="n">
-        <v>0.042625</v>
+        <v>3.963924</v>
       </c>
       <c r="M243" t="n">
-        <v>0.042625</v>
-      </c>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="n">
-        <v>0.3921500000000001</v>
-      </c>
-      <c r="P243" t="n">
-        <v>0.05967500000000001</v>
-      </c>
+        <v>1.2859004</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0.4214367999999999</v>
+      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
       <c r="Q243" t="n">
-        <v>15.287075</v>
-      </c>
-      <c r="R243" t="inlineStr"/>
-      <c r="S243" t="inlineStr"/>
+        <v>19.3112612</v>
+      </c>
+      <c r="R243" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="S243" t="n">
+        <v>1.86</v>
+      </c>
       <c r="T243" t="inlineStr"/>
-      <c r="U243" t="n">
-        <v>99.3</v>
-      </c>
+      <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
-      <c r="W243" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="W243" t="inlineStr"/>
       <c r="X243" t="n">
-        <v>42.33514999999999</v>
+        <v>51.4083808</v>
       </c>
       <c r="Y243" t="n">
-        <v>42.09645</v>
+        <v>19.7781672</v>
       </c>
       <c r="Z243" t="n">
-        <v>0.1705</v>
+        <v>7.555636400000001</v>
       </c>
       <c r="AA243" t="n">
-        <v>0.0682</v>
+        <v>1.4111224</v>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>工程科学学报煅烧白度篇原料</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>灰基准回收 | 高铝型(Al2O3 49.38)、高岭石99.3%；四目标和99.32+LOI14.75&gt;100 → 灰/灼烧基</t>
-        </is>
-      </c>
+      <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24739,17 +24837,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MDL-0394~C</t>
+          <t>MDL-0112~C</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>CSRC-ASH-005</t>
+          <t>CSRC-EXP-0019</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -24779,51 +24877,1825 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>西北J</t>
         </is>
       </c>
       <c r="K244" t="n">
-        <v>18.84999999999999</v>
-      </c>
-      <c r="L244" t="n">
-        <v>0.8277300000000001</v>
-      </c>
+        <v>26.98999999999999</v>
+      </c>
+      <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="n">
-        <v>19.67772999999999</v>
-      </c>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="S244" t="n">
+        <v>3.14</v>
+      </c>
       <c r="T244" t="inlineStr"/>
       <c r="U244" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" t="inlineStr"/>
       <c r="X244" t="n">
+        <v>39.5531675</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>13.8872321</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>2.5487791</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>1.0082681</v>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MDL-0113~C</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CSRC-EXP-0019</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="S245" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr"/>
+      <c r="W245" t="inlineStr"/>
+      <c r="X245" t="n">
+        <v>27.921136</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>15.4106112</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>1.4829792</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>0.9703231999999999</v>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>MDL-0114~C</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CSRC-EXP-0019</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="S246" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr"/>
+      <c r="W246" t="inlineStr"/>
+      <c r="X246" t="n">
+        <v>41.577284</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>17.683298</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>5.857808</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>1.55187</v>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>MDL-0117~C</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CSRC-EXP-0021</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>鄂尔多斯</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>西北J</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0.364119</v>
+      </c>
+      <c r="M247" t="n">
+        <v>0.423567</v>
+      </c>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="n">
+        <v>0.9140130000000001</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0.8991509999999999</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>28.29085</v>
+      </c>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr"/>
+      <c r="T247" t="inlineStr"/>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr"/>
+      <c r="W247" t="inlineStr"/>
+      <c r="X247" t="n">
+        <v>32.458608</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>36.679416</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>0.490446</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>1.092357</v>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>MDL-0132~C</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>CSRC-0120</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>朔州</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>洗选矸石</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>WASHED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="M248" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="n">
+        <v>0.6093000000000001</v>
+      </c>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="n">
+        <v>33.4509</v>
+      </c>
+      <c r="R248" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="S248" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T248" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="inlineStr"/>
+      <c r="W248" t="inlineStr"/>
+      <c r="X248" t="n">
+        <v>40.5523</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>21.4609</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>1.6925</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>2.0987</v>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>MDL-0133~C</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>CSRC-0120</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>忻州</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>洗选矸石</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>WASHED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L249" t="n">
+        <v>0.2154</v>
+      </c>
+      <c r="M249" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="n">
+        <v>30.4258</v>
+      </c>
+      <c r="R249" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="S249" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T249" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr"/>
+      <c r="W249" t="inlineStr"/>
+      <c r="X249" t="n">
+        <v>41.1414</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>16.2986</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>3.1592</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>6.6774</v>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>MDL-0134~C</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>CSRC-0120</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>吕梁</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>洗选矸石</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>WASHED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>31</v>
+      </c>
+      <c r="L250" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O250" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="n">
+        <v>33.484</v>
+      </c>
+      <c r="R250" t="n">
+        <v>69</v>
+      </c>
+      <c r="S250" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T250" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="U250" t="inlineStr"/>
+      <c r="V250" t="inlineStr"/>
+      <c r="W250" t="inlineStr"/>
+      <c r="X250" t="n">
+        <v>39.054</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>24.771</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>MDL-0135~C</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CSRC-0120</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>晋中</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>洗选矸石</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>WASHED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>26.90000000000001</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0.8771999999999999</v>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="n">
+        <v>0.8771999999999999</v>
+      </c>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="n">
+        <v>29.01990000000001</v>
+      </c>
+      <c r="R251" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="S251" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T251" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="inlineStr"/>
+      <c r="W251" t="inlineStr"/>
+      <c r="X251" t="n">
+        <v>46.1992</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>17.2516</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>4.824599999999999</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>1.2427</v>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>MDL-0136~C</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CSRC-0120</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>洗选矸石</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>WASHED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="L252" t="n">
+        <v>1.4278</v>
+      </c>
+      <c r="M252" t="n">
+        <v>1.1682</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0.7139000000000002</v>
+      </c>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="n">
+        <v>38.73439999999999</v>
+      </c>
+      <c r="R252" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="S252" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T252" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U252" t="inlineStr"/>
+      <c r="V252" t="inlineStr"/>
+      <c r="W252" t="inlineStr"/>
+      <c r="X252" t="n">
+        <v>35.69500000000001</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>18.8859</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>1.7523</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>3.6993</v>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MDL-0137~C</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CSRC-0120</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>临汾</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>洗选矸石</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>WASHED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>14.09999999999999</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="M253" t="n">
+        <v>2.0616</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0.9449000000000001</v>
+      </c>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="n">
+        <v>17.79369999999999</v>
+      </c>
+      <c r="R253" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="S253" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T253" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U253" t="inlineStr"/>
+      <c r="V253" t="inlineStr"/>
+      <c r="W253" t="inlineStr"/>
+      <c r="X253" t="n">
+        <v>54.20290000000001</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>24.13790000000001</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>2.0616</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>0.8590000000000001</v>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MDL-0138~C</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>CSRC-NEW-LPS-2014</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>六盘水</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>华南P2</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0.673248</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0.715326</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0.294546</v>
+      </c>
+      <c r="O254" t="n">
+        <v>1.802341</v>
+      </c>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="n">
+        <v>33.35546100000001</v>
+      </c>
+      <c r="R254" t="n">
+        <v>70.13</v>
+      </c>
+      <c r="S254" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T254" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U254" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="V254" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="W254" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="X254" t="n">
+        <v>29.672003</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>15.190158</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>5.477152999999999</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>1.598964</v>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MDL-0139~C</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>CSRC-NEW-LPS-2014</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>六盘水</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>华南P2</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="L255" t="n">
+        <v>1.192048</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0.6434350000000001</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0.8804900000000001</v>
+      </c>
+      <c r="O255" t="n">
+        <v>2.329912</v>
+      </c>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="n">
+        <v>37.31588499999999</v>
+      </c>
+      <c r="R255" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T255" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U255" t="n">
+        <v>8</v>
+      </c>
+      <c r="V255" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W255" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="X255" t="n">
+        <v>28.466919</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>11.818885</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>7.748311999999999</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>3.122353</v>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MDL-0140~C</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>CSRC-NEW-LPS-2014</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>六盘水</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>华南P2</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>20.70999999999999</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0.8484030000000001</v>
+      </c>
+      <c r="M256" t="n">
+        <v>1.292427</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0.126864</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0.6184620000000001</v>
+      </c>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="n">
+        <v>23.59615599999999</v>
+      </c>
+      <c r="R256" t="n">
+        <v>79.29000000000001</v>
+      </c>
+      <c r="S256" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="T256" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V256" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W256" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="X256" t="n">
+        <v>44.695773</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>16.325811</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>3.33018</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>0.261657</v>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr"/>
+      <c r="AD256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>MDL-0141~C</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>CSRC-NEW-LPS-2014</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>六盘水</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>煤巷矸/岩巷矸混合矸（矸石山采样）</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>华南P2</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>27.73999999999999</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0.852668</v>
+      </c>
+      <c r="M257" t="n">
+        <v>1.546364</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0.115616</v>
+      </c>
+      <c r="O257" t="n">
+        <v>1.828178</v>
+      </c>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="n">
+        <v>32.082826</v>
+      </c>
+      <c r="R257" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="S257" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T257" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U257" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="V257" t="inlineStr"/>
+      <c r="W257" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="X257" t="n">
+        <v>27.480478</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>11.135266</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>14.784396</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>1.091126</v>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>MDL-0176~C</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>CSRC-REM-0018</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>焦作</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>混合/未说明</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="S258" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="T258" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="U258" t="inlineStr"/>
+      <c r="V258" t="inlineStr"/>
+      <c r="W258" t="inlineStr"/>
+      <c r="X258" t="n">
+        <v>6.947811000000001</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>5.631718000000001</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>0.549638</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>0.319011</v>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr"/>
+      <c r="AD258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>MDL-0391~C</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>CSRC-ASH-002</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>晋中</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>华北C-P</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0.14546</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0.4654720000000001</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0.029092</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="n">
+        <v>28.346404</v>
+      </c>
+      <c r="R259" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="inlineStr"/>
+      <c r="U259" t="inlineStr"/>
+      <c r="V259" t="inlineStr"/>
+      <c r="W259" t="inlineStr"/>
+      <c r="X259" t="n">
+        <v>37.67414</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>21.542626</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>0.458199</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>0.09454900000000001</v>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>灵石县永恒煤化（9#/10#煤洗矸）</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>灰基准回收 | 表3-5工业(Ad72.73)+表3-6化学；四目标和82.18&gt;灰分+2 → 灰基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>MDL-0392~C</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CSRC-ASH-003</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>咸阳</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>西北J</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0.69025</v>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="n">
+        <v>0.8784999999999999</v>
+      </c>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="n">
+        <v>38.81875</v>
+      </c>
+      <c r="R260" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="S260" t="inlineStr"/>
+      <c r="T260" t="inlineStr"/>
+      <c r="U260" t="inlineStr"/>
+      <c r="V260" t="inlineStr"/>
+      <c r="W260" t="inlineStr"/>
+      <c r="X260" t="n">
+        <v>41.72875</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>12.9265</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>4.83175</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>1.69425</v>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>彬州陈家坪制砂原料矸</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>灰基准回收 | 灰分62.75+烧失量26.5；四目标和97.5&gt;灰分+2 → 灰基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>MDL-0393~C</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CSRC-ASH-004</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.042625</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0.042625</v>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="n">
+        <v>0.3921500000000001</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0.05967500000000001</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>15.287075</v>
+      </c>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="V261" t="inlineStr"/>
+      <c r="W261" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X261" t="n">
+        <v>42.33514999999999</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>42.09645</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>工程科学学报煅烧白度篇原料</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>灰基准回收 | 高铝型(Al2O3 49.38)、高岭石99.3%；四目标和99.32+LOI14.75&gt;100 → 灰/灼烧基</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>MDL-0394~C</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>CSRC-ASH-005</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>煤矸石</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>RAW_OR_UNSPECIFIED_GANGUE</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>18.84999999999999</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0.8277300000000001</v>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="n">
+        <v>19.67772999999999</v>
+      </c>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr"/>
+      <c r="V262" t="inlineStr"/>
+      <c r="W262" t="inlineStr"/>
+      <c r="X262" t="n">
         <v>49.32297000000001</v>
       </c>
-      <c r="Y244" t="n">
+      <c r="Y262" t="n">
         <v>22.162065</v>
       </c>
-      <c r="Z244" t="n">
+      <c r="Z262" t="n">
         <v>4.373985</v>
       </c>
-      <c r="AA244" t="n">
+      <c r="AA262" t="n">
         <v>0.30837</v>
       </c>
-      <c r="AB244" t="inlineStr">
+      <c r="AB262" t="inlineStr">
         <is>
           <t>converted</t>
         </is>
       </c>
-      <c r="AC244" t="inlineStr">
+      <c r="AC262" t="inlineStr">
         <is>
           <t>煤矸石-造纸污泥陶粒专利原料</t>
         </is>
       </c>
-      <c r="AD244" t="inlineStr">
+      <c r="AD262" t="inlineStr">
         <is>
           <t>灰基准回收 | 四目标93.86+烧失量18.85=112.71&gt;100 → 基准冲突</t>
         </is>
@@ -24840,7 +26712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24917,7 +26789,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>省 / 市</t>
+          <t>省 / 市（含美国宾夕法尼亚）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24978,34 +26850,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coalfield / coal_seam / coal_age</t>
+          <t>LOI烧失量</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>煤田 / 煤层 / 成煤时代</t>
+          <t>烧失量（GB/T 212 马弗炉 815℃）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>wt%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>地理地质</t>
+          <t>★入模特征</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOI烧失量</t>
+          <t>_den闭合分母</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>烧失量（GB/T 212 马弗炉 815℃）</t>
+          <t>MgO+K2O+Na2O+TiO2+SO3+LOI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -25022,12 +26894,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>_den闭合分母</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MgO+K2O+Na2O+TiO2+SO3+LOI</t>
+          <t>氧化钾（XRF）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -25044,12 +26916,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>MgO / Na2O / TiO2 / SO3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>氧化钾（XRF）</t>
+          <t>其他非目标氧化物（XRF）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -25059,63 +26931,63 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>★入模特征</t>
+          <t>构成 _den</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MgO / Na2O / TiO2 / SO3</t>
+          <t>灰分 / 水分 / 发热量</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>其他非目标氧化物（XRF）</t>
+          <t>工业分析</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wt%</t>
+          <t>wt% / wt% / MJ·kg⁻¹</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>构成 _den</t>
+          <t>备用</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>灰分 / 水分 / 发热量</t>
+          <t>高岭石 / 伊利石 / 石英</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>工业分析</t>
+          <t>XRD 矿物定量</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wt% / wt% / MJ·kg⁻¹</t>
+          <t>wt%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>备用</t>
+          <t>备用（Al2O3 建模用）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>高岭石 / 伊利石 / 石英</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XRD 矿物定量</t>
+          <t>★预测目标</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -25125,19 +26997,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>备用（Al2O3 建模用）</t>
+          <t>目标变量</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>Al2O3 / Fe2O3 / CaO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>★预测目标</t>
+          <t>其余三个目标（本包不建模）</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -25147,41 +27019,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>目标变量</t>
+          <t>参考</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Al2O3 / Fe2O3 / CaO</t>
+          <t>基准</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其余三个目标（本包不建模）</t>
+          <t>whole=整矸原值 / converted=灰基换算为整矸</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>wt%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>参考</t>
+          <t>口径</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>基准</t>
+          <t>矿名 / 来源备注</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole=整矸原值 / converted=灰基换算为整矸</t>
+          <t>溯源信息（文献/报告 + 表号）</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -25190,28 +27062,6 @@
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>矿名 / 来源备注</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>溯源信息（文献或报告 + 表号）</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
         <is>
           <t>溯源</t>
         </is>
@@ -25228,7 +27078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25371,107 +27221,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>56.43</v>
+        <v>42.01</v>
       </c>
       <c r="E6" t="n">
-        <v>7.81</v>
+        <v>14.18</v>
       </c>
       <c r="F6" t="n">
-        <v>41.73</v>
+        <v>26.7</v>
       </c>
       <c r="G6" t="n">
-        <v>68.98999999999999</v>
+        <v>71.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>54.19</v>
+        <v>56.43</v>
       </c>
       <c r="E7" t="n">
-        <v>5.63</v>
+        <v>7.81</v>
       </c>
       <c r="F7" t="n">
-        <v>48.73</v>
+        <v>41.73</v>
       </c>
       <c r="G7" t="n">
-        <v>65.58</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>46.44</v>
+        <v>54.19</v>
       </c>
       <c r="E8" t="n">
-        <v>6.16</v>
+        <v>5.63</v>
       </c>
       <c r="F8" t="n">
-        <v>33.26</v>
+        <v>48.73</v>
       </c>
       <c r="G8" t="n">
-        <v>51.85</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>57.01</v>
+        <v>46.44</v>
       </c>
       <c r="E9" t="n">
-        <v>6.61</v>
+        <v>6.16</v>
       </c>
       <c r="F9" t="n">
-        <v>51.41</v>
+        <v>33.26</v>
       </c>
       <c r="G9" t="n">
-        <v>68.51000000000001</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -25481,72 +27331,72 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>55.2</v>
+        <v>57.01</v>
       </c>
       <c r="E10" t="n">
-        <v>18.59</v>
+        <v>6.61</v>
       </c>
       <c r="F10" t="n">
-        <v>17.7</v>
+        <v>51.41</v>
       </c>
       <c r="G10" t="n">
-        <v>70.25</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>49.09</v>
+        <v>55.2</v>
       </c>
       <c r="E11" t="n">
-        <v>15.07</v>
+        <v>18.59</v>
       </c>
       <c r="F11" t="n">
-        <v>27.6</v>
+        <v>17.7</v>
       </c>
       <c r="G11" t="n">
-        <v>64.51000000000001</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>35.96</v>
+        <v>49.09</v>
       </c>
       <c r="E12" t="n">
-        <v>21.06</v>
+        <v>15.07</v>
       </c>
       <c r="F12" t="n">
-        <v>6.95</v>
+        <v>27.6</v>
       </c>
       <c r="G12" t="n">
-        <v>55.36</v>
+        <v>64.51000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -25556,16 +27406,16 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>57.18</v>
+        <v>35.96</v>
       </c>
       <c r="E13" t="n">
-        <v>6.02</v>
+        <v>21.06</v>
       </c>
       <c r="F13" t="n">
-        <v>48.16</v>
+        <v>6.95</v>
       </c>
       <c r="G13" t="n">
-        <v>60.63</v>
+        <v>55.36</v>
       </c>
     </row>
     <row r="14">
@@ -25596,32 +27446,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>60.45</v>
+        <v>57.18</v>
       </c>
       <c r="E15" t="n">
-        <v>3.12</v>
+        <v>6.02</v>
       </c>
       <c r="F15" t="n">
-        <v>58.3</v>
+        <v>48.16</v>
       </c>
       <c r="G15" t="n">
-        <v>64.03</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -25631,22 +27481,22 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>38.38</v>
+        <v>60.03</v>
       </c>
       <c r="E16" t="n">
-        <v>8.76</v>
+        <v>7.37</v>
       </c>
       <c r="F16" t="n">
-        <v>28.72</v>
+        <v>52.56</v>
       </c>
       <c r="G16" t="n">
-        <v>45.8</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -25656,47 +27506,47 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>60.03</v>
+        <v>38.38</v>
       </c>
       <c r="E17" t="n">
-        <v>7.37</v>
+        <v>8.76</v>
       </c>
       <c r="F17" t="n">
-        <v>52.56</v>
+        <v>28.72</v>
       </c>
       <c r="G17" t="n">
-        <v>67.3</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>匈牙利</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>48.12</v>
+        <v>64.13</v>
       </c>
       <c r="E18" t="n">
-        <v>3.38</v>
+        <v>6.96</v>
       </c>
       <c r="F18" t="n">
-        <v>46.14</v>
+        <v>59.2</v>
       </c>
       <c r="G18" t="n">
-        <v>52.03</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>匈牙利</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -25706,47 +27556,47 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>64.13</v>
+        <v>60.45</v>
       </c>
       <c r="E19" t="n">
-        <v>6.96</v>
+        <v>3.12</v>
       </c>
       <c r="F19" t="n">
-        <v>59.2</v>
+        <v>58.3</v>
       </c>
       <c r="G19" t="n">
-        <v>72.09999999999999</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>53.28</v>
+        <v>48.12</v>
       </c>
       <c r="E20" t="n">
-        <v>1.14</v>
+        <v>3.38</v>
       </c>
       <c r="F20" t="n">
-        <v>52.48</v>
+        <v>46.14</v>
       </c>
       <c r="G20" t="n">
-        <v>54.09</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>进口(未标注国别)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -25756,22 +27606,22 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>47.34</v>
+        <v>51.14</v>
       </c>
       <c r="E21" t="n">
-        <v>7.58</v>
+        <v>11.29</v>
       </c>
       <c r="F21" t="n">
-        <v>41.98</v>
+        <v>43.16</v>
       </c>
       <c r="G21" t="n">
-        <v>52.7</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>进口(未标注国别)</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -25781,70 +27631,72 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>51.14</v>
+        <v>53.28</v>
       </c>
       <c r="E22" t="n">
-        <v>11.29</v>
+        <v>1.14</v>
       </c>
       <c r="F22" t="n">
-        <v>43.16</v>
+        <v>52.48</v>
       </c>
       <c r="G22" t="n">
-        <v>59.12</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>47.11</v>
+        <v>47.34</v>
       </c>
       <c r="E23" t="n">
-        <v>24.05</v>
+        <v>7.58</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1</v>
+        <v>41.98</v>
       </c>
       <c r="G23" t="n">
-        <v>64.11</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>46.32</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>47.11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>24.05</v>
+      </c>
       <c r="F24" t="n">
-        <v>46.32</v>
+        <v>30.1</v>
       </c>
       <c r="G24" t="n">
-        <v>46.32</v>
+        <v>64.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -25854,20 +27706,20 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>71.98999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>71.98999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="G25" t="n">
-        <v>71.98999999999999</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -25877,20 +27729,20 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>59.9</v>
+        <v>46.32</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>59.9</v>
+        <v>46.32</v>
       </c>
       <c r="G26" t="n">
-        <v>59.9</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>河南(推测)</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -25900,13 +27752,36 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>48.54</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>71.98999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>河南(推测)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>48.54</v>
       </c>
-      <c r="G27" t="n">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="G28" t="n">
         <v>48.54</v>
       </c>
     </row>
@@ -25948,7 +27823,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -25961,10 +27836,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="4">
@@ -25974,10 +27849,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7893</v>
       </c>
     </row>
     <row r="5">
@@ -25987,10 +27862,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9506</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="6">
@@ -26000,10 +27875,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6513</v>
       </c>
     </row>
     <row r="7">
@@ -26013,10 +27888,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7613</v>
+        <v>0.7778</v>
       </c>
     </row>
     <row r="8">
@@ -26029,7 +27904,7 @@
         <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>0.428</v>
+        <v>0.3985</v>
       </c>
     </row>
     <row r="9">
@@ -26039,10 +27914,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2798</v>
+        <v>0.3295</v>
       </c>
     </row>
     <row r="10">
@@ -26055,7 +27930,7 @@
         <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3128</v>
+        <v>0.2912</v>
       </c>
     </row>
     <row r="11">
@@ -26068,7 +27943,7 @@
         <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2263</v>
+        <v>0.2107</v>
       </c>
     </row>
     <row r="12">
@@ -26081,7 +27956,7 @@
         <v>47</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1934</v>
+        <v>0.1801</v>
       </c>
     </row>
     <row r="13">
@@ -26094,7 +27969,7 @@
         <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1975</v>
+        <v>0.1839</v>
       </c>
     </row>
   </sheetData>
